--- a/data/BerkData3RAW.xlsx
+++ b/data/BerkData3RAW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_57D931A7D3D051338FDA3E11595ED87656CF7107" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC47695D-1D3E-4276-84B5-0EA67D0F1F1E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0BF9FA-CD7B-4693-8CE1-55393224E14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1545,6 +1545,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1572,20 +1586,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1600,12 +1600,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A8771978-B951-48EA-8B46-08D52B520CAF}" name="Table1" displayName="Table1" ref="A1:M294" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A8771978-B951-48EA-8B46-08D52B520CAF}" name="Table1" displayName="Table1" ref="A1:M294" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:M294" xr:uid="{A8771978-B951-48EA-8B46-08D52B520CAF}">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="2"/>
-        <filter val="3"/>
+        <filter val="PFE 202"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1914,22 +1913,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M294"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.73046875" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.9296875" customWidth="1"/>
-    <col min="5" max="5" width="18.9296875" customWidth="1"/>
-    <col min="7" max="7" width="11.06640625" customWidth="1"/>
-    <col min="9" max="9" width="11.19921875" customWidth="1"/>
-    <col min="10" max="10" width="11.73046875" customWidth="1"/>
+    <col min="1" max="1" width="17.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" customWidth="1"/>
+    <col min="5" max="5" width="27.08984375" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" customWidth="1"/>
+    <col min="9" max="9" width="11.1796875" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="16.265625" customWidth="1"/>
-    <col min="13" max="13" width="13.86328125" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2175,7 +2174,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2216,7 +2215,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2257,7 +2256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2626,7 +2625,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2749,7 +2748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2790,7 +2789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2831,7 +2830,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2954,7 +2953,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -2995,7 +2994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -3036,7 +3035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -3159,7 +3158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -3282,7 +3281,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -3323,7 +3322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3487,7 +3486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -3528,7 +3527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -3610,7 +3609,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -3733,7 +3732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -3815,7 +3814,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -3856,7 +3855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>36</v>
       </c>
@@ -3938,7 +3937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>28</v>
       </c>
@@ -3979,7 +3978,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -4020,7 +4019,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -4061,7 +4060,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -4102,7 +4101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -4143,7 +4142,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -4225,7 +4224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -4266,7 +4265,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>113</v>
       </c>
@@ -4307,7 +4306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -4348,7 +4347,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -4389,7 +4388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -4430,7 +4429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -4471,7 +4470,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>36</v>
       </c>
@@ -4553,7 +4552,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>36</v>
       </c>
@@ -4594,7 +4593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>31</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -4717,7 +4716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>113</v>
       </c>
@@ -4799,7 +4798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -4840,7 +4839,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -4881,7 +4880,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>31</v>
       </c>
@@ -4922,7 +4921,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -4963,7 +4962,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>31</v>
       </c>
@@ -5004,7 +5003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -5045,7 +5044,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -5086,7 +5085,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -5127,7 +5126,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -5168,7 +5167,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>31</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -5250,7 +5249,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5291,7 +5290,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -5332,7 +5331,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>31</v>
       </c>
@@ -5373,7 +5372,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -5414,7 +5413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>36</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -5496,7 +5495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -5537,7 +5536,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -5578,7 +5577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -5619,7 +5618,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -5660,7 +5659,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -5701,7 +5700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -5742,7 +5741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>36</v>
       </c>
@@ -5783,7 +5782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -5824,7 +5823,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>31</v>
       </c>
@@ -5865,7 +5864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -5906,7 +5905,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>24</v>
       </c>
@@ -5947,7 +5946,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -5988,7 +5987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>31</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -6070,7 +6069,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>28</v>
       </c>
@@ -6111,7 +6110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>36</v>
       </c>
@@ -6152,7 +6151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>24</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>26</v>
       </c>
@@ -6234,7 +6233,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>26</v>
       </c>
@@ -6275,7 +6274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>26</v>
       </c>
@@ -6316,7 +6315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>26</v>
       </c>
@@ -6357,7 +6356,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>26</v>
       </c>
@@ -6398,7 +6397,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>26</v>
       </c>
@@ -6439,7 +6438,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>26</v>
       </c>
@@ -6480,7 +6479,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -6521,7 +6520,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>26</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>26</v>
       </c>
@@ -6603,7 +6602,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>28</v>
       </c>
@@ -6685,7 +6684,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>28</v>
       </c>
@@ -6726,7 +6725,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>31</v>
       </c>
@@ -6767,7 +6766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>31</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>36</v>
       </c>
@@ -6890,7 +6889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>31</v>
       </c>
@@ -6931,7 +6930,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -6972,7 +6971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>36</v>
       </c>
@@ -7013,7 +7012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -7054,7 +7053,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -7095,7 +7094,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -7136,7 +7135,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -7177,7 +7176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -7218,7 +7217,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -7259,7 +7258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>28</v>
       </c>
@@ -7300,7 +7299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>28</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>28</v>
       </c>
@@ -7382,7 +7381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>31</v>
       </c>
@@ -7423,7 +7422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>31</v>
       </c>
@@ -7464,7 +7463,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -7546,7 +7545,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>21</v>
       </c>
@@ -7587,7 +7586,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>31</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>24</v>
       </c>
@@ -7669,7 +7668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -7710,7 +7709,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -7751,7 +7750,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>26</v>
       </c>
@@ -7792,7 +7791,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>21</v>
       </c>
@@ -7833,7 +7832,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>36</v>
       </c>
@@ -7874,7 +7873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>31</v>
       </c>
@@ -7915,7 +7914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>31</v>
       </c>
@@ -7956,7 +7955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>24</v>
       </c>
@@ -7997,7 +7996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -8038,7 +8037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -8079,7 +8078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>26</v>
       </c>
@@ -8120,7 +8119,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>13</v>
       </c>
@@ -8161,7 +8160,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>113</v>
       </c>
@@ -8202,7 +8201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -8243,7 +8242,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>36</v>
       </c>
@@ -8284,7 +8283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>26</v>
       </c>
@@ -8325,7 +8324,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>31</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>24</v>
       </c>
@@ -8407,7 +8406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>21</v>
       </c>
@@ -8448,7 +8447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>21</v>
       </c>
@@ -8489,7 +8488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -8530,7 +8529,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>28</v>
       </c>
@@ -8571,7 +8570,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -8612,7 +8611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>21</v>
       </c>
@@ -8653,7 +8652,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>31</v>
       </c>
@@ -8694,7 +8693,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>24</v>
       </c>
@@ -8735,7 +8734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>24</v>
       </c>
@@ -8776,7 +8775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>31</v>
       </c>
@@ -8817,7 +8816,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>31</v>
       </c>
@@ -8858,7 +8857,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>21</v>
       </c>
@@ -8899,7 +8898,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>24</v>
       </c>
@@ -8940,7 +8939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>31</v>
       </c>
@@ -8981,7 +8980,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -9022,7 +9021,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>28</v>
       </c>
@@ -9063,7 +9062,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -9104,7 +9103,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>113</v>
       </c>
@@ -9145,7 +9144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>36</v>
       </c>
@@ -9186,7 +9185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>31</v>
       </c>
@@ -9227,7 +9226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>31</v>
       </c>
@@ -9268,7 +9267,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>24</v>
       </c>
@@ -9309,7 +9308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>28</v>
       </c>
@@ -9350,7 +9349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -9391,7 +9390,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>28</v>
       </c>
@@ -9432,7 +9431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>28</v>
       </c>
@@ -9473,7 +9472,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>21</v>
       </c>
@@ -9514,7 +9513,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>24</v>
       </c>
@@ -9555,7 +9554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -9596,7 +9595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -9637,7 +9636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>21</v>
       </c>
@@ -9678,7 +9677,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>31</v>
       </c>
@@ -9719,7 +9718,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>31</v>
       </c>
@@ -9760,7 +9759,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>31</v>
       </c>
@@ -9801,7 +9800,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -9842,7 +9841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>21</v>
       </c>
@@ -9883,7 +9882,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>36</v>
       </c>
@@ -9924,7 +9923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>24</v>
       </c>
@@ -9965,7 +9964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -10006,7 +10005,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>31</v>
       </c>
@@ -10047,7 +10046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>28</v>
       </c>
@@ -10088,7 +10087,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -10129,7 +10128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>21</v>
       </c>
@@ -10170,7 +10169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>31</v>
       </c>
@@ -10211,7 +10210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>28</v>
       </c>
@@ -10252,7 +10251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -10293,7 +10292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -10334,7 +10333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>21</v>
       </c>
@@ -10375,7 +10374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>31</v>
       </c>
@@ -10416,7 +10415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -10457,7 +10456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -10498,7 +10497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -10539,7 +10538,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -10580,7 +10579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>28</v>
       </c>
@@ -10621,7 +10620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -10662,7 +10661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>28</v>
       </c>
@@ -10744,7 +10743,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -10785,7 +10784,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>113</v>
       </c>
@@ -10826,7 +10825,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>36</v>
       </c>
@@ -10867,7 +10866,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -10908,7 +10907,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>113</v>
       </c>
@@ -10949,7 +10948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>28</v>
       </c>
@@ -10990,7 +10989,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>28</v>
       </c>
@@ -11031,7 +11030,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -11072,7 +11071,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>28</v>
       </c>
@@ -11113,7 +11112,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>28</v>
       </c>
@@ -11154,7 +11153,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -11195,7 +11194,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>26</v>
       </c>
@@ -11236,7 +11235,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>28</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>26</v>
       </c>
@@ -11318,7 +11317,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>13</v>
       </c>
@@ -11359,7 +11358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>31</v>
       </c>
@@ -11400,7 +11399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>24</v>
       </c>
@@ -11441,7 +11440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>31</v>
       </c>
@@ -11482,7 +11481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>36</v>
       </c>
@@ -11523,7 +11522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>24</v>
       </c>
@@ -11564,7 +11563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>28</v>
       </c>
@@ -11605,7 +11604,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>13</v>
       </c>
@@ -11646,7 +11645,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -11687,7 +11686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -11728,7 +11727,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>31</v>
       </c>
@@ -11769,7 +11768,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>13</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>13</v>
       </c>
@@ -11851,7 +11850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>21</v>
       </c>
@@ -11892,7 +11891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>31</v>
       </c>
@@ -11933,7 +11932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>28</v>
       </c>
@@ -11974,7 +11973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>26</v>
       </c>
@@ -12015,7 +12014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>13</v>
       </c>
@@ -12056,7 +12055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>13</v>
       </c>
@@ -12097,7 +12096,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>26</v>
       </c>
@@ -12138,7 +12137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>21</v>
       </c>
@@ -12179,7 +12178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>31</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>21</v>
       </c>
@@ -12261,7 +12260,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>31</v>
       </c>
@@ -12302,7 +12301,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>36</v>
       </c>
@@ -12343,7 +12342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>24</v>
       </c>
@@ -12384,7 +12383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>21</v>
       </c>
@@ -12425,7 +12424,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>21</v>
       </c>
@@ -12466,7 +12465,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -12507,7 +12506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>31</v>
       </c>
@@ -12548,7 +12547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>36</v>
       </c>
@@ -12589,7 +12588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>31</v>
       </c>
@@ -12630,7 +12629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -12671,7 +12670,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>21</v>
       </c>
@@ -12712,7 +12711,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -12753,7 +12752,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>36</v>
       </c>
@@ -12794,7 +12793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>26</v>
       </c>
@@ -12835,7 +12834,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>31</v>
       </c>
@@ -12876,7 +12875,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>36</v>
       </c>
@@ -12917,7 +12916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>13</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>21</v>
       </c>
@@ -12999,7 +12998,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>21</v>
       </c>
@@ -13040,7 +13039,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>28</v>
       </c>
@@ -13081,7 +13080,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>13</v>
       </c>
@@ -13122,7 +13121,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>113</v>
       </c>
@@ -13163,7 +13162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>21</v>
       </c>
@@ -13204,7 +13203,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>36</v>
       </c>
@@ -13245,7 +13244,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>31</v>
       </c>
@@ -13286,7 +13285,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>24</v>
       </c>
@@ -13327,7 +13326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>26</v>
       </c>
@@ -13368,7 +13367,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>24</v>
       </c>
@@ -13409,7 +13408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>26</v>
       </c>
@@ -13450,7 +13449,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>28</v>
       </c>
@@ -13491,7 +13490,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -13532,7 +13531,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>36</v>
       </c>
@@ -13573,7 +13572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -13614,7 +13613,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>31</v>
       </c>
@@ -13655,7 +13654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>21</v>
       </c>
@@ -13696,7 +13695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>21</v>
       </c>
@@ -13737,7 +13736,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>21</v>
       </c>
@@ -13778,7 +13777,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>24</v>
       </c>
@@ -13819,7 +13818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>21</v>
       </c>
@@ -13860,7 +13859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>21</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>24</v>
       </c>
@@ -13942,7 +13941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>21</v>
       </c>
